--- a/Result/profitability/8121.xlsx
+++ b/Result/profitability/8121.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>-0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02</v>
+        <v>-0.06125000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>17.5425</v>
+        <v>16.7375</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -684,10 +684,10 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.25</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0175</v>
+        <v>-0.01125000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>17.43375</v>
+        <v>18.1475</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.23</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03</v>
+        <v>0.02999999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>18.4</v>
+        <v>18.59375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.007499999999999993</v>
+        <v>0.03</v>
       </c>
       <c r="N5" t="n">
-        <v>17.5425</v>
+        <v>17.81</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.78</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05500000000000001</v>
+        <v>-0.065</v>
       </c>
       <c r="N6" t="n">
-        <v>13.86375</v>
+        <v>13.91375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.11375</v>
+        <v>-0.1375</v>
       </c>
       <c r="N7" t="n">
-        <v>11.85375</v>
+        <v>11.475</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>-0.15</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.14375</v>
+        <v>-0.16875</v>
       </c>
       <c r="N8" t="n">
-        <v>11.00375</v>
+        <v>10.66625</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8121</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>892</v>
+      </c>
+      <c r="D75" t="n">
+        <v>743</v>
+      </c>
+      <c r="E75" t="n">
+        <v>149</v>
+      </c>
+      <c r="F75" t="n">
+        <v>16.73</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-0.63%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-21</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.02875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>17.02625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.699999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1389603705609881</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6428571428571428</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.140000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1466758053461275</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
